--- a/lead_generation_forms/020_digital_seo_referral_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/020_digital_seo_referral_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'google'}</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Google'}</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'google_ads'}</t>
+          <t>google_ads</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Google Ads'}</t>
+          <t>Google Ads</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'facebook_ads'}</t>
+          <t>facebook_ads</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Facebook Ads'}</t>
+          <t>Facebook Ads</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'word_of_mouth'}</t>
+          <t>word_of_mouth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Word of Mouth'}</t>
+          <t>Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Social Media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'referral'}</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Referral'}</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'website'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Website'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'print_media'}</t>
+          <t>print_media</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Print Media'}</t>
+          <t>Print Media</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'qualified'}</t>
+          <t>qualified</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Qualified'}</t>
+          <t>Qualified</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'referred'}</t>
+          <t>referred</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Referred'}</t>
+          <t>Referred</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'converted'}</t>
+          <t>converted</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'Converted'}</t>
+          <t>Converted</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'lost'}</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'Lost'}</t>
+          <t>Lost</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'new_lead'}</t>
+          <t>new_lead</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'New Lead'}</t>
+          <t>New Lead</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'existing_client'}</t>
+          <t>existing_client</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'Existing Client'}</t>
+          <t>Existing Client</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'hot_lead'}</t>
+          <t>hot_lead</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'Hot Lead'}</t>
+          <t>Hot Lead</t>
         </is>
       </c>
     </row>
